--- a/RelatorioProjetoDA_Modelo_Kelly_Joao_Bianca.xlsx
+++ b/RelatorioProjetoDA_Modelo_Kelly_Joao_Bianca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kelly\Documents\ProjetoDA2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22AB2C4-27B5-4715-B13F-02D7A86CD40E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E300FD-CFAC-4A92-92E7-835E192F7CA1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="gM3we6J0DihOXhhsVCVKEXQOkV9atHBEZEgMEOHliw2f+IhL1XhdH2iU/lWL6zpI42wRp6vwQ5IcaeTeZHIQSg==" workbookSaltValue="GQxFLs+f58FLaT3gnUsMQg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="73">
   <si>
     <t>Elementos do Grupo:</t>
   </si>
@@ -160,9 +160,6 @@
     <t>F4</t>
   </si>
   <si>
-    <t>Selecione uma opção...</t>
-  </si>
-  <si>
     <t>Nota: Preencher todos os campos AZUIS até à linha com o texto "FIM"</t>
   </si>
   <si>
@@ -302,6 +299,27 @@
   </si>
   <si>
     <t>Completo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> João Rodrigo Dias Moreira</t>
+  </si>
+  <si>
+    <t>Foi implementado um password hash para a maior proteção dos dados do utilizador.</t>
+  </si>
+  <si>
+    <t>Password hash</t>
+  </si>
+  <si>
+    <t>Possivel criar, editar e eliminar os tipos de artigo</t>
+  </si>
+  <si>
+    <t>Possivel criar, editar e eliminar os artigos</t>
+  </si>
+  <si>
+    <t>Possivel criar, editar e eliminar orçamentos</t>
+  </si>
+  <si>
+    <t>Acesso a todas as forms, grelha mostra compras em aberto, botão modo compra para abrir a compra selecionada.</t>
   </si>
 </sst>
 </file>
@@ -771,32 +789,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -810,21 +815,89 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
@@ -837,66 +910,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2162,7 +2180,7 @@
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="I4" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:9" s="5" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2181,28 +2199,28 @@
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
+      <c r="B7" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
     </row>
     <row r="8" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
     </row>
     <row r="9" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8"/>
@@ -2219,17 +2237,17 @@
       <c r="B11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="50"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="48"/>
       <c r="I11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2262,12 +2280,12 @@
       <c r="E15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="53"/>
+      <c r="F15" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="51"/>
     </row>
     <row r="16" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
@@ -2279,93 +2297,97 @@
       <c r="E16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
+      <c r="F16" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="51"/>
     </row>
     <row r="17" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="20"/>
+      <c r="C17" s="20">
+        <v>2025187039</v>
+      </c>
       <c r="E17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="53"/>
+      <c r="F17" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="51"/>
     </row>
     <row r="18" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+    </row>
+    <row r="20" spans="2:9" s="11" customFormat="1" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-    </row>
-    <row r="20" spans="2:9" s="11" customFormat="1" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
     </row>
     <row r="21" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
+      <c r="B21" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
     </row>
     <row r="22" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
+      <c r="B23" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
     </row>
     <row r="24" spans="2:9" s="11" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
@@ -2376,81 +2398,83 @@
       <c r="E24" s="19"/>
     </row>
     <row r="25" spans="2:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
+      <c r="B25" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
     </row>
     <row r="27" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
+      <c r="B27" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
     </row>
     <row r="28" spans="2:9" s="11" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
     </row>
     <row r="29" spans="2:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
     </row>
     <row r="30" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="7"/>
     </row>
     <row r="31" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
+      <c r="B31" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
     </row>
     <row r="32" spans="2:9" s="11" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
     </row>
     <row r="33" spans="2:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
     </row>
     <row r="34" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="21"/>
@@ -2475,278 +2499,288 @@
       <c r="I36" s="37"/>
     </row>
     <row r="37" spans="2:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
     </row>
     <row r="38" spans="2:9" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
     </row>
     <row r="39" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="33"/>
+    </row>
+    <row r="40" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="26"/>
+      <c r="C40" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
+    </row>
+    <row r="41" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="31"/>
-    </row>
-    <row r="40" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="27"/>
-      <c r="C40" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="33"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="36"/>
-    </row>
-    <row r="41" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="28" t="s">
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="30" t="s">
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="33"/>
+    </row>
+    <row r="42" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="26"/>
+      <c r="C42" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="28"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="24"/>
+    </row>
+    <row r="43" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="33"/>
+    </row>
+    <row r="44" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="26"/>
+      <c r="C44" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="28"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="24"/>
+    </row>
+    <row r="45" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="33"/>
+    </row>
+    <row r="46" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="26"/>
+      <c r="C46" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="35"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="56"/>
+    </row>
+    <row r="47" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="33"/>
+    </row>
+    <row r="48" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="26"/>
+      <c r="C48" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="28"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" s="23"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="24"/>
+    </row>
+    <row r="49" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="33"/>
+    </row>
+    <row r="50" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="26"/>
+      <c r="C50" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="28"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="24"/>
+    </row>
+    <row r="51" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="31"/>
-    </row>
-    <row r="42" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="27"/>
-      <c r="C42" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="36"/>
-    </row>
-    <row r="43" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="31"/>
-    </row>
-    <row r="44" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="27"/>
-      <c r="C44" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" s="33"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="36"/>
-    </row>
-    <row r="45" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="31"/>
-    </row>
-    <row r="46" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="27"/>
-      <c r="C46" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="56"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="41"/>
-    </row>
-    <row r="47" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="30" t="s">
+      <c r="C51" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="31"/>
-    </row>
-    <row r="48" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="27"/>
-      <c r="C48" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="33"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="36"/>
-    </row>
-    <row r="49" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="30" t="s">
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="33"/>
+    </row>
+    <row r="52" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="26"/>
+      <c r="C52" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="28"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="24"/>
+    </row>
+    <row r="53" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="31"/>
-    </row>
-    <row r="50" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="27"/>
-      <c r="C50" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="33"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="36"/>
-    </row>
-    <row r="51" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="31"/>
-    </row>
-    <row r="52" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="27"/>
-      <c r="C52" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="33"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="36"/>
-    </row>
-    <row r="53" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="26" t="s">
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="33"/>
+    </row>
+    <row r="54" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="26"/>
+      <c r="C54" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="28"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="24"/>
+    </row>
+    <row r="55" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C55" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="30" t="s">
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="31"/>
-    </row>
-    <row r="54" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="27"/>
-      <c r="C54" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D54" s="33"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="36"/>
-    </row>
-    <row r="55" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="31"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="33"/>
     </row>
     <row r="56" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="27"/>
-      <c r="C56" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="33"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="36"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="28"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="24"/>
     </row>
     <row r="57" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="4"/>
@@ -2759,7 +2793,7 @@
     </row>
     <row r="58" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C58" s="37"/>
       <c r="D58" s="37"/>
@@ -2770,197 +2804,186 @@
       <c r="I58" s="37"/>
     </row>
     <row r="59" spans="2:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="25" t="s">
+      <c r="B59" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="25"/>
-      <c r="I59" s="25"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
     </row>
     <row r="60" spans="2:9" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
     </row>
     <row r="61" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="26" t="s">
+      <c r="B61" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="C61" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="30" t="s">
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="33"/>
+    </row>
+    <row r="62" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="26"/>
+      <c r="C62" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="28"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="24"/>
+    </row>
+    <row r="63" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="33"/>
+    </row>
+    <row r="64" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="26"/>
+      <c r="C64" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="28"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="24"/>
+    </row>
+    <row r="65" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="31"/>
-    </row>
-    <row r="62" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="27"/>
-      <c r="C62" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D62" s="33"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="36"/>
-    </row>
-    <row r="63" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G63" s="30"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="31"/>
-    </row>
-    <row r="64" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="27"/>
-      <c r="C64" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D64" s="33"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="36"/>
-    </row>
-    <row r="65" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="28" t="s">
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="30" t="s">
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="33"/>
+    </row>
+    <row r="66" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="26"/>
+      <c r="C66" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" s="28"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="23"/>
+      <c r="H66" s="23"/>
+      <c r="I66" s="24"/>
+    </row>
+    <row r="67" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="31"/>
-    </row>
-    <row r="66" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="27"/>
-      <c r="C66" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D66" s="33"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="36"/>
-    </row>
-    <row r="67" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="28" t="s">
+      <c r="C67" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="31"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="33"/>
     </row>
     <row r="68" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="27"/>
-      <c r="C68" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D68" s="33"/>
-      <c r="E68" s="34"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="36"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="28"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="70" spans="2:9" s="13" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="23" t="s">
+      <c r="B70" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
     </row>
   </sheetData>
   <sheetProtection insertHyperlinks="0" selectLockedCells="1"/>
   <mergeCells count="91">
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F67:I67"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B70:I70"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="F46:I46"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="F49:I49"/>
@@ -2977,38 +3000,49 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="F41:I41"/>
     <mergeCell ref="C42:E42"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="B70:I70"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B59:I59"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="B63:B64"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C39:E40">

--- a/RelatorioProjetoDA_Modelo_Kelly_Joao_Bianca.xlsx
+++ b/RelatorioProjetoDA_Modelo_Kelly_Joao_Bianca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kelly\Documents\ProjetoDA2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E300FD-CFAC-4A92-92E7-835E192F7CA1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6017DA-06EC-4A89-9CC7-6E79DFAC0D83}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="gM3we6J0DihOXhhsVCVKEXQOkV9atHBEZEgMEOHliw2f+IhL1XhdH2iU/lWL6zpI42wRp6vwQ5IcaeTeZHIQSg==" workbookSaltValue="GQxFLs+f58FLaT3gnUsMQg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -789,6 +789,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
@@ -797,35 +836,73 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -838,83 +915,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2199,28 +2199,28 @@
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
     </row>
     <row r="8" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8"/>
@@ -2237,10 +2237,10 @@
       <c r="B11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="51"/>
       <c r="I11" s="2" t="s">
         <v>19</v>
       </c>
@@ -2276,16 +2276,18 @@
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20"/>
+      <c r="C15" s="20">
+        <v>2025165248</v>
+      </c>
       <c r="E15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="49" t="s">
+      <c r="F15" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="54"/>
     </row>
     <row r="16" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
@@ -2297,12 +2299,12 @@
       <c r="E16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="54"/>
     </row>
     <row r="17" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
@@ -2314,80 +2316,80 @@
       <c r="E17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="51"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="54"/>
     </row>
     <row r="18" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
     </row>
     <row r="19" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="2:9" s="11" customFormat="1" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
     </row>
     <row r="21" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
     </row>
     <row r="23" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="2:9" s="11" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
@@ -2398,65 +2400,65 @@
       <c r="E24" s="19"/>
     </row>
     <row r="25" spans="2:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="27" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="2:9" s="11" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="2:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="7"/>
     </row>
     <row r="31" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
     </row>
     <row r="32" spans="2:9" s="11" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="12" t="s">
@@ -2467,14 +2469,14 @@
       <c r="E32" s="19"/>
     </row>
     <row r="33" spans="2:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="21"/>
@@ -2499,288 +2501,288 @@
       <c r="I36" s="37"/>
     </row>
     <row r="37" spans="2:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" spans="2:9" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
     </row>
     <row r="39" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32" t="s">
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="31"/>
     </row>
     <row r="40" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="26"/>
-      <c r="C40" s="27" t="s">
+      <c r="B40" s="27"/>
+      <c r="C40" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="23" t="s">
+      <c r="D40" s="33"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="24"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="36"/>
     </row>
     <row r="41" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="32" t="s">
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="33"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="31"/>
     </row>
     <row r="42" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="26"/>
-      <c r="C42" s="27" t="s">
+      <c r="B42" s="27"/>
+      <c r="C42" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="28"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="23" t="s">
+      <c r="D42" s="33"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="24"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="36"/>
     </row>
     <row r="43" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="32" t="s">
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="33"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="31"/>
     </row>
     <row r="44" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="26"/>
-      <c r="C44" s="27" t="s">
+      <c r="B44" s="27"/>
+      <c r="C44" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="28"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="23" t="s">
+      <c r="D44" s="33"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="24"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="36"/>
     </row>
     <row r="45" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="38" t="s">
+      <c r="B45" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="32" t="s">
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="33"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="31"/>
     </row>
     <row r="46" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="26"/>
-      <c r="C46" s="34" t="s">
+      <c r="B46" s="27"/>
+      <c r="C46" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="35"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="54" t="s">
+      <c r="D46" s="57"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="56"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="41"/>
     </row>
     <row r="47" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32" t="s">
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="33"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="31"/>
     </row>
     <row r="48" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="26"/>
-      <c r="C48" s="27" t="s">
+      <c r="B48" s="27"/>
+      <c r="C48" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D48" s="28"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="23" t="s">
+      <c r="D48" s="33"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="23"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="24"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="36"/>
     </row>
     <row r="49" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="32" t="s">
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="33"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="31"/>
     </row>
     <row r="50" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="26"/>
-      <c r="C50" s="27" t="s">
+      <c r="B50" s="27"/>
+      <c r="C50" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D50" s="28"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="24"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="36"/>
     </row>
     <row r="51" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="30" t="s">
+      <c r="C51" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="32" t="s">
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="33"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="31"/>
     </row>
     <row r="52" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="26"/>
-      <c r="C52" s="27" t="s">
+      <c r="B52" s="27"/>
+      <c r="C52" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="28"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="24"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="36"/>
     </row>
     <row r="53" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C53" s="30" t="s">
+      <c r="C53" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="32" t="s">
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="33"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="31"/>
     </row>
     <row r="54" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="26"/>
-      <c r="C54" s="27" t="s">
+      <c r="B54" s="27"/>
+      <c r="C54" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="28"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="24"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="36"/>
     </row>
     <row r="55" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="32" t="s">
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="33"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="31"/>
     </row>
     <row r="56" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="26"/>
-      <c r="C56" s="27" t="s">
+      <c r="B56" s="27"/>
+      <c r="C56" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D56" s="28"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="24"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="36"/>
     </row>
     <row r="57" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="4"/>
@@ -2804,154 +2806,229 @@
       <c r="I58" s="37"/>
     </row>
     <row r="59" spans="2:9" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="53" t="s">
+      <c r="B59" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="53"/>
-      <c r="D59" s="53"/>
-      <c r="E59" s="53"/>
-      <c r="F59" s="53"/>
-      <c r="G59" s="53"/>
-      <c r="H59" s="53"/>
-      <c r="I59" s="53"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
     </row>
     <row r="60" spans="2:9" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="58"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="32" t="s">
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="33"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="31"/>
     </row>
     <row r="62" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="26"/>
-      <c r="C62" s="27" t="s">
+      <c r="B62" s="27"/>
+      <c r="C62" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D62" s="28"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="24"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="36"/>
     </row>
     <row r="63" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="30" t="s">
+      <c r="C63" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="32" t="s">
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="33"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="31"/>
     </row>
     <row r="64" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="26"/>
-      <c r="C64" s="27" t="s">
+      <c r="B64" s="27"/>
+      <c r="C64" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D64" s="28"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="24"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="36"/>
     </row>
     <row r="65" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C65" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="32" t="s">
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="33"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="31"/>
     </row>
     <row r="66" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="26"/>
-      <c r="C66" s="27" t="s">
+      <c r="B66" s="27"/>
+      <c r="C66" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="28"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="23"/>
-      <c r="I66" s="24"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="36"/>
     </row>
     <row r="67" spans="2:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C67" s="30" t="s">
+      <c r="C67" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="32" t="s">
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="33"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="31"/>
     </row>
     <row r="68" spans="2:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="26"/>
-      <c r="C68" s="27" t="s">
+      <c r="B68" s="27"/>
+      <c r="C68" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D68" s="28"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="24"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="36"/>
     </row>
     <row r="70" spans="2:9" s="13" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="57" t="s">
+      <c r="B70" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
+      <c r="I70" s="23"/>
     </row>
   </sheetData>
   <sheetProtection insertHyperlinks="0" selectLockedCells="1"/>
   <mergeCells count="91">
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="F46:I46"/>
     <mergeCell ref="B70:I70"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="B59:I59"/>
@@ -2968,81 +3045,6 @@
     <mergeCell ref="C63:E63"/>
     <mergeCell ref="F63:I63"/>
     <mergeCell ref="C64:E64"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F67:I67"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="B63:B64"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C39:E40">
